--- a/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
+++ b/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FC9AE36-BC86-4BB7-B83B-492EFAD46ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26EBAB53-EE5A-451C-879A-BE92EA68732C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="23" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="22" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="21" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="20" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="19" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="28" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="27" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="26" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="25" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="24" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94119DE6-3E26-C222-F165-C09E608BD56B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95F6EA2C-8E0F-97DA-AAA9-AA91632907A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5241,7 +5241,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA17D6D-FAFA-6BDA-4C7F-67FF13A5A612}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3363482C-573D-27E4-5B7D-C568CF0364A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33AED0A8-267D-47DF-95C0-8CA4521075AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE61D04A-F292-4D98-B337-162EE3056CE7}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8720,7 +8720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED7A1C75-3567-4C85-8FCD-9EBFCCB7D4D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3686D0-D61E-49AE-9DAC-F21A4314BCF2}">
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9680,7 +9680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C485130-4036-42BC-9200-CC0F25ABE9B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9D4AADE-8F5E-49D4-871B-168B98DF6436}">
   <dimension ref="B2:J245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16742,7 +16742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87FA069C-3DA1-42F4-8C6F-175DEF8C3FAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E60AB2-2138-4699-81A7-1471E5C01F3F}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17320,7 +17320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{610F4EEB-223F-4DE8-9746-9BF643B2937D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941AF082-667C-477D-B2B2-22591F426F11}">
   <dimension ref="A1:Y595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -33994,7 +33994,7 @@
         <v>748</v>
       </c>
       <c r="B299" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C299" t="s">
         <v>33</v>
@@ -34006,7 +34006,7 @@
         <v>2024</v>
       </c>
       <c r="I299" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J299" t="s">
         <v>121</v>
@@ -34015,7 +34015,7 @@
         <v>122</v>
       </c>
       <c r="L299">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="M299">
         <v>1610</v>
@@ -34027,7 +34027,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P299">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="R299">
         <v>38</v>
@@ -34059,7 +34059,7 @@
         <v>748</v>
       </c>
       <c r="B300" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C300" t="s">
         <v>33</v>
@@ -34071,7 +34071,7 @@
         <v>2024</v>
       </c>
       <c r="I300" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J300" t="s">
         <v>121</v>
@@ -34080,7 +34080,7 @@
         <v>122</v>
       </c>
       <c r="L300">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="M300">
         <v>1610</v>
@@ -34092,7 +34092,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P300">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R300">
         <v>38</v>
@@ -35034,7 +35034,7 @@
         <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C315" t="s">
         <v>33</v>
@@ -35046,7 +35046,7 @@
         <v>2023</v>
       </c>
       <c r="I315" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -35058,16 +35058,16 @@
         <v>0.1</v>
       </c>
       <c r="M315">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="N315">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="O315">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P315">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R315">
         <v>38</v>
@@ -35099,7 +35099,7 @@
         <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -35111,7 +35111,7 @@
         <v>2023</v>
       </c>
       <c r="I316" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -35123,16 +35123,16 @@
         <v>0.1</v>
       </c>
       <c r="M316">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="N316">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="O316">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P316">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="R316">
         <v>38</v>

--- a/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
+++ b/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26EBAB53-EE5A-451C-879A-BE92EA68732C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{700417D3-19ED-47A2-A1B1-36B0F1D537AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="28" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="27" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="26" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="25" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="24" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="33" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="32" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="31" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="30" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="29" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95F6EA2C-8E0F-97DA-AAA9-AA91632907A2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04A80E6F-837C-4131-9B91-A3535F5EFAE9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5241,7 +5241,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3363482C-573D-27E4-5B7D-C568CF0364A8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEE220A9-4B1A-0D2B-333A-8BC43630DF51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE61D04A-F292-4D98-B337-162EE3056CE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BDFDB0-DC5C-4857-8FEF-4852A7CB9427}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8720,7 +8720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3686D0-D61E-49AE-9DAC-F21A4314BCF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A680F32C-C98F-4965-B2E6-F341257688EF}">
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9680,7 +9680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9D4AADE-8F5E-49D4-871B-168B98DF6436}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B32A47B-3EF7-4DD9-BEE3-9B8ACE76FA14}">
   <dimension ref="B2:J245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16742,7 +16742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E60AB2-2138-4699-81A7-1471E5C01F3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D611E2-1B57-4A4D-A242-7EEBF1E62889}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17320,7 +17320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941AF082-667C-477D-B2B2-22591F426F11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07112FAB-D20E-4921-BC40-D4027D127CC1}">
   <dimension ref="A1:Y595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -33994,7 +33994,7 @@
         <v>748</v>
       </c>
       <c r="B299" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C299" t="s">
         <v>33</v>
@@ -34006,7 +34006,7 @@
         <v>2024</v>
       </c>
       <c r="I299" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J299" t="s">
         <v>121</v>
@@ -34015,7 +34015,7 @@
         <v>122</v>
       </c>
       <c r="L299">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="M299">
         <v>1610</v>
@@ -34027,7 +34027,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P299">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R299">
         <v>38</v>
@@ -34059,7 +34059,7 @@
         <v>748</v>
       </c>
       <c r="B300" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C300" t="s">
         <v>33</v>
@@ -34071,7 +34071,7 @@
         <v>2024</v>
       </c>
       <c r="I300" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J300" t="s">
         <v>121</v>
@@ -34080,7 +34080,7 @@
         <v>122</v>
       </c>
       <c r="L300">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="M300">
         <v>1610</v>
@@ -34092,7 +34092,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P300">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="R300">
         <v>38</v>
@@ -35034,7 +35034,7 @@
         <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C315" t="s">
         <v>33</v>
@@ -35046,7 +35046,7 @@
         <v>2023</v>
       </c>
       <c r="I315" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -35058,16 +35058,16 @@
         <v>0.1</v>
       </c>
       <c r="M315">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="N315">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="O315">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P315">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="R315">
         <v>38</v>
@@ -35099,7 +35099,7 @@
         <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -35111,7 +35111,7 @@
         <v>2023</v>
       </c>
       <c r="I316" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -35123,16 +35123,16 @@
         <v>0.1</v>
       </c>
       <c r="M316">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="N316">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="O316">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P316">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R316">
         <v>38</v>

--- a/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
+++ b/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{700417D3-19ED-47A2-A1B1-36B0F1D537AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E46E8462-8A72-4C02-B14D-B6CBC7C2C612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="33" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="32" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="31" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="30" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="29" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="38" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="37" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="36" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="35" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="34" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04A80E6F-837C-4131-9B91-A3535F5EFAE9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C940142C-D2E7-C683-186F-B22EEE4B66BA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5241,7 +5241,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEE220A9-4B1A-0D2B-333A-8BC43630DF51}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B24AFFBB-7371-DCBC-A312-F3C63589FAD8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BDFDB0-DC5C-4857-8FEF-4852A7CB9427}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9323D915-C455-4F7B-A6B2-3EBFF5839FC0}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8720,7 +8720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A680F32C-C98F-4965-B2E6-F341257688EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A31AF1-BBD2-4FA0-85E7-14C2C9ADF020}">
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9680,7 +9680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B32A47B-3EF7-4DD9-BEE3-9B8ACE76FA14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B24E06-E32B-4E56-8568-90AE4650CF6D}">
   <dimension ref="B2:J245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16742,7 +16742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D611E2-1B57-4A4D-A242-7EEBF1E62889}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6EA2D5-6B5F-44E5-9E64-EC900D860660}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17320,7 +17320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07112FAB-D20E-4921-BC40-D4027D127CC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{281D4C9D-FE99-43E2-8138-27AC19910CDE}">
   <dimension ref="A1:Y595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35034,7 +35034,7 @@
         <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C315" t="s">
         <v>33</v>
@@ -35046,7 +35046,7 @@
         <v>2023</v>
       </c>
       <c r="I315" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -35058,16 +35058,16 @@
         <v>0.1</v>
       </c>
       <c r="M315">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="N315">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="O315">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P315">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R315">
         <v>38</v>
@@ -35099,7 +35099,7 @@
         <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -35111,7 +35111,7 @@
         <v>2023</v>
       </c>
       <c r="I316" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -35123,16 +35123,16 @@
         <v>0.1</v>
       </c>
       <c r="M316">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="N316">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="O316">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P316">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="R316">
         <v>38</v>
@@ -49703,7 +49703,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q571">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016432</v>
       </c>
     </row>
     <row r="572" spans="1:25" x14ac:dyDescent="0.25">
@@ -49738,7 +49738,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q572">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016432</v>
       </c>
     </row>
     <row r="573" spans="1:25" x14ac:dyDescent="0.25">
@@ -49773,7 +49773,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q573">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016432</v>
       </c>
     </row>
     <row r="574" spans="1:25" x14ac:dyDescent="0.25">

--- a/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
+++ b/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E46E8462-8A72-4C02-B14D-B6CBC7C2C612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A516018E-8445-4061-8048-C7610F284AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="38" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="37" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="36" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="35" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="34" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="43" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="42" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="41" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="40" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="39" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C940142C-D2E7-C683-186F-B22EEE4B66BA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC6508FC-D18C-FD24-888E-12E8E6B80D90}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5241,7 +5241,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B24AFFBB-7371-DCBC-A312-F3C63589FAD8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DADA91C6-2577-6922-1058-FD9DEE0247AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9323D915-C455-4F7B-A6B2-3EBFF5839FC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E65A9D-B5D0-4E5A-BE0D-4CA223FDD142}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8720,7 +8720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A31AF1-BBD2-4FA0-85E7-14C2C9ADF020}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42803B40-EC47-4917-8C0B-71AF5B8ACBFB}">
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9680,7 +9680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B24E06-E32B-4E56-8568-90AE4650CF6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2961C446-1CE9-447B-956F-FCAC17632BF3}">
   <dimension ref="B2:J245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16742,7 +16742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6EA2D5-6B5F-44E5-9E64-EC900D860660}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CB3252-28B7-4FBB-A8BD-134C623A5361}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17320,7 +17320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{281D4C9D-FE99-43E2-8138-27AC19910CDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97611881-BB7D-4B6A-87A5-BA64AD00F603}">
   <dimension ref="A1:Y595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -33994,7 +33994,7 @@
         <v>748</v>
       </c>
       <c r="B299" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C299" t="s">
         <v>33</v>
@@ -34006,7 +34006,7 @@
         <v>2024</v>
       </c>
       <c r="I299" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J299" t="s">
         <v>121</v>
@@ -34015,7 +34015,7 @@
         <v>122</v>
       </c>
       <c r="L299">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="M299">
         <v>1610</v>
@@ -34027,7 +34027,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P299">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="R299">
         <v>38</v>
@@ -34059,7 +34059,7 @@
         <v>748</v>
       </c>
       <c r="B300" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C300" t="s">
         <v>33</v>
@@ -34071,7 +34071,7 @@
         <v>2024</v>
       </c>
       <c r="I300" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J300" t="s">
         <v>121</v>
@@ -34080,7 +34080,7 @@
         <v>122</v>
       </c>
       <c r="L300">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="M300">
         <v>1610</v>
@@ -34092,7 +34092,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P300">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R300">
         <v>38</v>
@@ -35034,7 +35034,7 @@
         <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C315" t="s">
         <v>33</v>
@@ -35046,7 +35046,7 @@
         <v>2023</v>
       </c>
       <c r="I315" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -35058,16 +35058,16 @@
         <v>0.1</v>
       </c>
       <c r="M315">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="N315">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="O315">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P315">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="R315">
         <v>38</v>
@@ -35099,7 +35099,7 @@
         <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -35111,7 +35111,7 @@
         <v>2023</v>
       </c>
       <c r="I316" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -35123,16 +35123,16 @@
         <v>0.1</v>
       </c>
       <c r="M316">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="N316">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="O316">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P316">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R316">
         <v>38</v>

--- a/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
+++ b/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A516018E-8445-4061-8048-C7610F284AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA404763-3321-42DF-A740-A4B6CEB4175B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="43" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="42" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="41" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="40" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="39" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="48" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="47" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="46" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="45" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="44" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC6508FC-D18C-FD24-888E-12E8E6B80D90}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEAD4220-625A-192A-CBD5-848381987F72}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5241,7 +5241,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DADA91C6-2577-6922-1058-FD9DEE0247AB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FAFC9A9-3130-CCA8-C617-2313DAF34515}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E65A9D-B5D0-4E5A-BE0D-4CA223FDD142}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9E8916-D80A-4859-BF80-20FD9915EE50}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8720,7 +8720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42803B40-EC47-4917-8C0B-71AF5B8ACBFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06783C80-5621-41F7-B4D0-5578ED4AD34F}">
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9680,7 +9680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2961C446-1CE9-447B-956F-FCAC17632BF3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4BBE91-6DC4-48ED-9212-7164BED35C33}">
   <dimension ref="B2:J245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16742,7 +16742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CB3252-28B7-4FBB-A8BD-134C623A5361}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D9F8BB-13B8-40EF-ABC7-042CFD44BADD}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17320,7 +17320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97611881-BB7D-4B6A-87A5-BA64AD00F603}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63DB57A-E93A-48BF-849B-5C9ABC6C3450}">
   <dimension ref="A1:Y595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35034,7 +35034,7 @@
         <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C315" t="s">
         <v>33</v>
@@ -35046,7 +35046,7 @@
         <v>2023</v>
       </c>
       <c r="I315" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -35058,16 +35058,16 @@
         <v>0.1</v>
       </c>
       <c r="M315">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="N315">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="O315">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P315">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R315">
         <v>38</v>
@@ -35099,7 +35099,7 @@
         <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -35111,7 +35111,7 @@
         <v>2023</v>
       </c>
       <c r="I316" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -35123,16 +35123,16 @@
         <v>0.1</v>
       </c>
       <c r="M316">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="N316">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="O316">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P316">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="R316">
         <v>38</v>
@@ -49703,7 +49703,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q571">
-        <v>0.19280418494016432</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="572" spans="1:25" x14ac:dyDescent="0.25">
@@ -49738,7 +49738,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q572">
-        <v>0.19280418494016432</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="573" spans="1:25" x14ac:dyDescent="0.25">
@@ -49773,7 +49773,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q573">
-        <v>0.19280418494016432</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="574" spans="1:25" x14ac:dyDescent="0.25">

--- a/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
+++ b/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA404763-3321-42DF-A740-A4B6CEB4175B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8612272E-0B6B-4AD5-B768-1CEDA8B2FD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="48" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="47" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="46" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="45" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="44" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="53" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="52" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="51" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="50" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="49" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEAD4220-625A-192A-CBD5-848381987F72}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{633D7FF2-91E3-7A04-1822-5D1159461F2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5241,7 +5241,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FAFC9A9-3130-CCA8-C617-2313DAF34515}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E05FC229-2EE8-407F-82E5-DC8381398063}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9E8916-D80A-4859-BF80-20FD9915EE50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939CD415-EA1B-4875-9EBF-AE5AE1E85E7E}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8720,7 +8720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06783C80-5621-41F7-B4D0-5578ED4AD34F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8A8F8A-DA74-4C42-8101-5E431915D8DC}">
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9680,7 +9680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4BBE91-6DC4-48ED-9212-7164BED35C33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7A7ADF-BC92-4079-9E29-2ADFC3D32512}">
   <dimension ref="B2:J245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16742,7 +16742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D9F8BB-13B8-40EF-ABC7-042CFD44BADD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0025A64-CC21-4375-BFA5-4581C62C7E5D}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17320,7 +17320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63DB57A-E93A-48BF-849B-5C9ABC6C3450}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE3C99C-6624-4C86-BF98-77D2D66587D0}">
   <dimension ref="A1:Y595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35034,7 +35034,7 @@
         <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C315" t="s">
         <v>33</v>
@@ -35046,7 +35046,7 @@
         <v>2023</v>
       </c>
       <c r="I315" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -35058,16 +35058,16 @@
         <v>0.1</v>
       </c>
       <c r="M315">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="N315">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="O315">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P315">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="R315">
         <v>38</v>
@@ -35099,7 +35099,7 @@
         <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -35111,7 +35111,7 @@
         <v>2023</v>
       </c>
       <c r="I316" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -35123,16 +35123,16 @@
         <v>0.1</v>
       </c>
       <c r="M316">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="N316">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="O316">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P316">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R316">
         <v>38</v>

--- a/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
+++ b/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8612272E-0B6B-4AD5-B768-1CEDA8B2FD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA7A892F-999D-4D4C-B5FD-9A4E008A36B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="53" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="52" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="51" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="50" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="49" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="58" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="57" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="56" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="55" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="54" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{633D7FF2-91E3-7A04-1822-5D1159461F2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB0F0D61-F08C-7AAD-5AB9-25D1B43E21AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5241,7 +5241,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E05FC229-2EE8-407F-82E5-DC8381398063}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7D3D0EB-51D8-D4B3-85AA-645927E34E26}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939CD415-EA1B-4875-9EBF-AE5AE1E85E7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F99A0C-E309-46BB-BEC4-F5F3AAA8EFF1}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8720,7 +8720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8A8F8A-DA74-4C42-8101-5E431915D8DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA13A333-EF67-4390-B6F1-E1FDCD80BDDB}">
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9680,7 +9680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7A7ADF-BC92-4079-9E29-2ADFC3D32512}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7420FE16-90E0-49A4-A117-5D2F3F04AAAE}">
   <dimension ref="B2:J245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16742,7 +16742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0025A64-CC21-4375-BFA5-4581C62C7E5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{772D62B7-8ED4-473F-AF10-DFA22A383213}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17320,7 +17320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE3C99C-6624-4C86-BF98-77D2D66587D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F2A4CC-1094-46FB-A1D5-CBAB1A4EC02C}">
   <dimension ref="A1:Y595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35034,7 +35034,7 @@
         <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C315" t="s">
         <v>33</v>
@@ -35046,7 +35046,7 @@
         <v>2023</v>
       </c>
       <c r="I315" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -35058,16 +35058,16 @@
         <v>0.1</v>
       </c>
       <c r="M315">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="N315">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="O315">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P315">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R315">
         <v>38</v>
@@ -35099,7 +35099,7 @@
         <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -35111,7 +35111,7 @@
         <v>2023</v>
       </c>
       <c r="I316" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -35123,16 +35123,16 @@
         <v>0.1</v>
       </c>
       <c r="M316">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="N316">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="O316">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P316">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="R316">
         <v>38</v>

--- a/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
+++ b/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA7A892F-999D-4D4C-B5FD-9A4E008A36B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F24468F9-46F1-49C6-9E69-682C0454477C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="58" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="57" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="56" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="55" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="54" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="63" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="62" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="61" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="60" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="59" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB0F0D61-F08C-7AAD-5AB9-25D1B43E21AC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F006B868-6D08-4767-3F01-96CCB6EF3308}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5241,7 +5241,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7D3D0EB-51D8-D4B3-85AA-645927E34E26}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C483EC00-A63C-EA2B-44EA-85AFFEDEFBCF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F99A0C-E309-46BB-BEC4-F5F3AAA8EFF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F23EB7-F6CC-4100-ACB8-2BCBF2196B4F}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8720,7 +8720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA13A333-EF67-4390-B6F1-E1FDCD80BDDB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04D2720-BB1F-421E-8D6C-FD0DA3565228}">
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9680,7 +9680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7420FE16-90E0-49A4-A117-5D2F3F04AAAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C179064E-1EBC-47E8-916E-9D6BE8E38EA2}">
   <dimension ref="B2:J245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16742,7 +16742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{772D62B7-8ED4-473F-AF10-DFA22A383213}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A7897D-1ABD-4777-AD35-38C8D61B86BA}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17320,7 +17320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F2A4CC-1094-46FB-A1D5-CBAB1A4EC02C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F10FA70-7ADA-4304-B718-CF09F0C6216D}">
   <dimension ref="A1:Y595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -33994,7 +33994,7 @@
         <v>748</v>
       </c>
       <c r="B299" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C299" t="s">
         <v>33</v>
@@ -34006,7 +34006,7 @@
         <v>2024</v>
       </c>
       <c r="I299" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J299" t="s">
         <v>121</v>
@@ -34015,7 +34015,7 @@
         <v>122</v>
       </c>
       <c r="L299">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="M299">
         <v>1610</v>
@@ -34027,7 +34027,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P299">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R299">
         <v>38</v>
@@ -34059,7 +34059,7 @@
         <v>748</v>
       </c>
       <c r="B300" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C300" t="s">
         <v>33</v>
@@ -34071,7 +34071,7 @@
         <v>2024</v>
       </c>
       <c r="I300" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J300" t="s">
         <v>121</v>
@@ -34080,7 +34080,7 @@
         <v>122</v>
       </c>
       <c r="L300">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="M300">
         <v>1610</v>
@@ -34092,7 +34092,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P300">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="R300">
         <v>38</v>
@@ -35034,7 +35034,7 @@
         <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C315" t="s">
         <v>33</v>
@@ -35046,7 +35046,7 @@
         <v>2023</v>
       </c>
       <c r="I315" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -35058,16 +35058,16 @@
         <v>0.1</v>
       </c>
       <c r="M315">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="N315">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="O315">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P315">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="R315">
         <v>38</v>
@@ -35099,7 +35099,7 @@
         <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -35111,7 +35111,7 @@
         <v>2023</v>
       </c>
       <c r="I316" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -35123,16 +35123,16 @@
         <v>0.1</v>
       </c>
       <c r="M316">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="N316">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="O316">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P316">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R316">
         <v>38</v>
@@ -49703,7 +49703,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q571">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016441</v>
       </c>
     </row>
     <row r="572" spans="1:25" x14ac:dyDescent="0.25">
@@ -49738,7 +49738,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q572">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016441</v>
       </c>
     </row>
     <row r="573" spans="1:25" x14ac:dyDescent="0.25">
@@ -49773,7 +49773,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q573">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016441</v>
       </c>
     </row>
     <row r="574" spans="1:25" x14ac:dyDescent="0.25">

--- a/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
+++ b/VerveStacks_IDN_grids_kan/source_data/VerveStacks_IDN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F24468F9-46F1-49C6-9E69-682C0454477C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2449B569-E374-47E9-BDC4-83CC3867E053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="63" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="62" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="61" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="60" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="59" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="68" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="67" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="66" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="65" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="64" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F006B868-6D08-4767-3F01-96CCB6EF3308}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A5823C7-6521-075C-639E-90FC26C4BEF3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5241,7 +5241,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C483EC00-A63C-EA2B-44EA-85AFFEDEFBCF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE694369-B90B-E872-22BE-751989E68FAE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F23EB7-F6CC-4100-ACB8-2BCBF2196B4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44F29B0B-B3A2-4C7D-9731-FAEE0EFFEAEA}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8720,7 +8720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04D2720-BB1F-421E-8D6C-FD0DA3565228}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94275ECB-8691-4499-BD72-7A1E2763C002}">
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9680,7 +9680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C179064E-1EBC-47E8-916E-9D6BE8E38EA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04649CCB-B4C0-48C5-B78B-16E5B994B9DC}">
   <dimension ref="B2:J245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16742,7 +16742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A7897D-1ABD-4777-AD35-38C8D61B86BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F4FEBDA-A960-4DAE-A72A-F9E6A36C1410}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -17320,7 +17320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F10FA70-7ADA-4304-B718-CF09F0C6216D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11850E1-1052-484A-95AB-6DC7DBFD04CB}">
   <dimension ref="A1:Y595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -33994,7 +33994,7 @@
         <v>748</v>
       </c>
       <c r="B299" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C299" t="s">
         <v>33</v>
@@ -34006,7 +34006,7 @@
         <v>2024</v>
       </c>
       <c r="I299" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J299" t="s">
         <v>121</v>
@@ -34015,7 +34015,7 @@
         <v>122</v>
       </c>
       <c r="L299">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="M299">
         <v>1610</v>
@@ -34027,7 +34027,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P299">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="R299">
         <v>38</v>
@@ -34059,7 +34059,7 @@
         <v>748</v>
       </c>
       <c r="B300" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C300" t="s">
         <v>33</v>
@@ -34071,7 +34071,7 @@
         <v>2024</v>
       </c>
       <c r="I300" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J300" t="s">
         <v>121</v>
@@ -34080,7 +34080,7 @@
         <v>122</v>
       </c>
       <c r="L300">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="M300">
         <v>1610</v>
@@ -34092,7 +34092,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P300">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R300">
         <v>38</v>
@@ -35034,7 +35034,7 @@
         <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C315" t="s">
         <v>33</v>
@@ -35046,7 +35046,7 @@
         <v>2023</v>
       </c>
       <c r="I315" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -35058,16 +35058,16 @@
         <v>0.1</v>
       </c>
       <c r="M315">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="N315">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="O315">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P315">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="R315">
         <v>38</v>
@@ -35099,7 +35099,7 @@
         <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C316" t="s">
         <v>33</v>
@@ -35111,7 +35111,7 @@
         <v>2023</v>
       </c>
       <c r="I316" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -35123,16 +35123,16 @@
         <v>0.1</v>
       </c>
       <c r="M316">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="N316">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="O316">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P316">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="R316">
         <v>38</v>
@@ -49703,7 +49703,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q571">
-        <v>0.19280418494016441</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="572" spans="1:25" x14ac:dyDescent="0.25">
@@ -49738,7 +49738,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q572">
-        <v>0.19280418494016441</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="573" spans="1:25" x14ac:dyDescent="0.25">
@@ -49773,7 +49773,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q573">
-        <v>0.19280418494016441</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="574" spans="1:25" x14ac:dyDescent="0.25">
